--- a/data/processed/auditoria_cpts.xlsx
+++ b/data/processed/auditoria_cpts.xlsx
@@ -18,7 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Renta" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especializacion_Servicios" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dinamismo_Demografico" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Viabilidad_Empresarial" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Densidad" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Juventud" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanidad" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paro" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Viabilidad_Empresarial" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -506,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.333333333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -536,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3.333333333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -566,13 +570,13 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.666666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -596,13 +600,13 @@
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3703703703703703</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -626,13 +630,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.111111111111111</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="F6" t="n">
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -656,13 +660,13 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3703703703703703</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -686,13 +690,13 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3703703703703703</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -701,12 +705,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Viabilidad_Empresarial</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dinamismo_Demografico, Especializacion_Servicios</t>
+          <t>Coste_Inmobiliario, Distancia_Madrid</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -716,15 +720,135 @@
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3703703703703703</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="F9" t="n">
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Densidad, Distancia_Madrid</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sanidad</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Paro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Distancia_Madrid, Renta</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="F12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Viabilidad_Empresarial</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Densidad, Dinamismo_Demografico</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -750,11 +874,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,25 +972,25 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4162062615101289</v>
+        <v>0.4012066365007541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.565377532228361</v>
+        <v>0.5233785822021115</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01841620626151013</v>
+        <v>0.07541478129713423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4162062615101289</v>
+        <v>0.4012066365007542</v>
       </c>
       <c r="K2" t="n">
-        <v>0.565377532228361</v>
+        <v>0.5233785822021116</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01841620626151013</v>
+        <v>0.07541478129713425</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="3">
@@ -893,25 +1017,25 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="H3" t="n">
-        <v>0.767816091954023</v>
+        <v>0.6738738738738738</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08505747126436781</v>
+        <v>0.1387387387387387</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="K3" t="n">
-        <v>0.767816091954023</v>
+        <v>0.6738738738738739</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08505747126436781</v>
+        <v>0.1387387387387388</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="4">
@@ -938,22 +1062,22 @@
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01366120218579235</v>
+        <v>0.05868544600938967</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05054644808743169</v>
+        <v>0.09037558685446009</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9357923497267759</v>
+        <v>0.8509389671361501</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01366120218579235</v>
+        <v>0.05868544600938967</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05054644808743169</v>
+        <v>0.09037558685446009</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9357923497267759</v>
+        <v>0.8509389671361501</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -983,25 +1107,25 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.581159420289855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1596491228070175</v>
+        <v>0.1898550724637681</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2070175438596491</v>
+        <v>0.2289855072463768</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5811594202898551</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1596491228070175</v>
+        <v>0.1898550724637681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2070175438596491</v>
+        <v>0.2289855072463768</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="6">
@@ -1028,25 +1152,25 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06491228070175438</v>
+        <v>0.1115942028985507</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5859649122807018</v>
+        <v>0.5420289855072463</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3491228070175438</v>
+        <v>0.3463768115942029</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06491228070175438</v>
+        <v>0.1115942028985507</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5859649122807018</v>
+        <v>0.5420289855072464</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3491228070175438</v>
+        <v>0.3463768115942029</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="7">
@@ -1073,22 +1197,22 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06813996316758747</v>
+        <v>0.1161387631975867</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1178637200736648</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8139963167587477</v>
+        <v>0.726998491704374</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06813996316758747</v>
+        <v>0.1161387631975867</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1178637200736648</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8139963167587477</v>
+        <v>0.726998491704374</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1118,25 +1242,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7855946398659966</v>
+        <v>0.709902370990237</v>
       </c>
       <c r="H8" t="n">
-        <v>0.152428810720268</v>
+        <v>0.1827057182705718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06197654941373534</v>
+        <v>0.1073919107391911</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7855946398659966</v>
+        <v>0.7099023709902371</v>
       </c>
       <c r="K8" t="n">
-        <v>0.152428810720268</v>
+        <v>0.1827057182705719</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06197654941373534</v>
+        <v>0.1073919107391911</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="9">
@@ -1163,25 +1287,25 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4528023598820059</v>
+        <v>0.4348370927318295</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4528023598820059</v>
+        <v>0.4348370927318295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0943952802359882</v>
+        <v>0.1303258145363408</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4528023598820059</v>
+        <v>0.4348370927318296</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4528023598820059</v>
+        <v>0.4348370927318296</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0943952802359882</v>
+        <v>0.1303258145363409</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="10">
@@ -1208,25 +1332,25 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4574712643678161</v>
+        <v>0.4306306306306306</v>
       </c>
       <c r="H10" t="n">
-        <v>0.271264367816092</v>
+        <v>0.2846846846846847</v>
       </c>
       <c r="I10" t="n">
-        <v>0.271264367816092</v>
+        <v>0.2846846846846847</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4574712643678161</v>
+        <v>0.4306306306306306</v>
       </c>
       <c r="K10" t="n">
-        <v>0.271264367816092</v>
+        <v>0.2846846846846847</v>
       </c>
       <c r="L10" t="n">
-        <v>0.271264367816092</v>
+        <v>0.2846846846846847</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
   </sheetData>
@@ -1251,11 +1375,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1349,22 +1473,22 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3878787878787879</v>
+        <v>0.3649122807017544</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5515151515151515</v>
+        <v>0.4596491228070176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3878787878787879</v>
+        <v>0.3649122807017544</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5515151515151515</v>
+        <v>0.4596491228070176</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1394,25 +1518,25 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09068627450980392</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4877450980392157</v>
+        <v>0.4526515151515151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4215686274509804</v>
+        <v>0.4015151515151515</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09068627450980392</v>
+        <v>0.1458333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4877450980392157</v>
+        <v>0.4526515151515151</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4215686274509804</v>
+        <v>0.4015151515151515</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="4">
@@ -1439,22 +1563,22 @@
         <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2225153913808267</v>
+        <v>0.2330946698488464</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2225153913808267</v>
+        <v>0.2330946698488464</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5549692172383465</v>
+        <v>0.5338106603023071</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2225153913808267</v>
+        <v>0.2330946698488464</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2225153913808267</v>
+        <v>0.2330946698488464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5549692172383465</v>
+        <v>0.5338106603023071</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1484,25 +1608,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6278118609406953</v>
+        <v>0.5697865353037767</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3517382413087934</v>
+        <v>0.348111658456486</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02044989775051125</v>
+        <v>0.08210180623973727</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6278118609406953</v>
+        <v>0.5697865353037767</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3517382413087934</v>
+        <v>0.3481116584564861</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02044989775051125</v>
+        <v>0.08210180623973728</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="6">
@@ -1529,19 +1653,19 @@
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1910408432147563</v>
+        <v>0.2104664391353811</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4756258234519104</v>
+        <v>0.4562002275312855</v>
       </c>
       <c r="I6" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1910408432147563</v>
+        <v>0.2104664391353811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4756258234519104</v>
+        <v>0.4562002275312855</v>
       </c>
       <c r="L6" t="n">
         <v>0.3333333333333333</v>
@@ -1619,22 +1743,22 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5719696969696969</v>
+        <v>0.5476190476190476</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1884469696969697</v>
+        <v>0.2032312925170068</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2491496598639455</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5719696969696969</v>
+        <v>0.5476190476190476</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1884469696969697</v>
+        <v>0.2032312925170068</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.2491496598639455</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1664,25 +1788,25 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2286821705426356</v>
+        <v>0.2484276729559748</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3856589147286822</v>
+        <v>0.3757861635220126</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3856589147286822</v>
+        <v>0.3757861635220126</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2286821705426356</v>
+        <v>0.2484276729559749</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3856589147286822</v>
+        <v>0.3757861635220126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3856589147286822</v>
+        <v>0.3757861635220126</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="10">
@@ -1709,25 +1833,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2681159420289855</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.463768115942029</v>
+        <v>0.4031007751937985</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2681159420289855</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2681159420289855</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="K10" t="n">
-        <v>0.463768115942029</v>
+        <v>0.4031007751937984</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2681159420289855</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1744,8 +1868,1220 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coste_Inmobiliario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distancia_Madrid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_municipios</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Baja</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Media</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Alta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Baja</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Media</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Alta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Baja</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Media</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Alta</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>max_dif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1754385964912281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2701754385964912</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5543859649122808</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.175438596491228</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2701754385964912</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5543859649122806</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3503787878787878</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5549242424242423</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0946969696969697</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3503787878787879</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5549242424242424</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.09469696969696971</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8130469371519491</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1256961018297534</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06125696101829754</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.813046937151949</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1256961018297534</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06125696101829753</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08210180623973727</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3037766830870279</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6141215106732347</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.08210180623973727</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3037766830870279</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6141215106732347</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3640500568828213</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5176336746302617</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.118316268486917</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3640500568828213</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5176336746302617</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.118316268486917</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4792792792792792</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1387387387387387</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4792792792792793</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1387387387387388</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>38</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04251700680272109</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2261904761904762</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7312925170068026</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.04251700680272109</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2261904761904762</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7312925170068026</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.07861635220125786</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.460691823899371</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.460691823899371</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.07861635220125787</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4606918238993711</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4606918238993711</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2984496124031008</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4031007751937985</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2984496124031008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2984496124031008</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4031007751937984</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2984496124031008</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distancia_Madrid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_municipios</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Baja</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Media</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Alta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Baja</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Media</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Alta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Baja</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Media</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Alta</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>max_dif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.236036036036036</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.381981981981982</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.236036036036036</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8476190476190476</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.09597069597069598</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05641025641025641</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8476190476190475</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.09597069597069596</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0564102564102564</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0946969696969697</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2992424242424243</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.606060606060606</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0946969696969697</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2992424242424243</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.606060606060606</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1258405379442843</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4370797310278578</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4370797310278578</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1258405379442843</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4370797310278578</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4370797310278578</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2763713080168776</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5042194092827004</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2194092827004219</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2763713080168777</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5042194092827005</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.219409282700422</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cerca</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.09410919540229885</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3462643678160919</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5596264367816092</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.09410919540229885</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3462643678160919</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5596264367816092</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2930648769574944</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4742729306487695</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.232662192393736</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2930648769574944</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4742729306487695</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.232662192393736</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4502164502164502</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2164502164502164</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4502164502164502</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2164502164502164</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n_municipios</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Baja</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Media</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Alta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Baja</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Media</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Alta</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Baja</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Media</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Alta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>max_dif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.346376811594203</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1115942028985507</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5420289855072464</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3463768115942029</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1115942028985507</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5420289855072463</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2980910425844347</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4170337738619678</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2848751835535977</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2980910425844346</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4170337738619677</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2848751835535976</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3594202898550725</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1768115942028986</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3594202898550725</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1768115942028985</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1756,18 +3092,18 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dinamismo_Demografico</t>
+          <t>Distancia_Madrid</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Especializacion_Servicios</t>
+          <t>Renta</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1777,47 +3113,47 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>conteo_Baja</t>
+          <t>conteo_Bajo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>conteo_Media</t>
+          <t>conteo_Medio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>conteo_Alta</t>
+          <t>conteo_Alto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>P_manual_Baja</t>
+          <t>P_manual_Bajo</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>P_manual_Media</t>
+          <t>P_manual_Medio</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>P_manual_Alta</t>
+          <t>P_manual_Alto</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>P_pgmpy_Baja</t>
+          <t>P_pgmpy_Bajo</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>P_pgmpy_Media</t>
+          <t>P_pgmpy_Medio</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>P_pgmpy_Alta</t>
+          <t>P_pgmpy_Alto</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1829,7 +3165,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Cerca</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1838,43 +3174,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.722943722943723</v>
+        <v>0.09980039920159679</v>
       </c>
       <c r="H2" t="n">
-        <v>0.196969696969697</v>
+        <v>0.4770459081836327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08008658008658008</v>
+        <v>0.4231536926147704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.722943722943723</v>
+        <v>0.09980039920159682</v>
       </c>
       <c r="K2" t="n">
-        <v>0.196969696969697</v>
+        <v>0.4770459081836327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08008658008658008</v>
+        <v>0.4231536926147705</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Cerca</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1886,40 +3222,40 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5352564102564102</v>
+        <v>0.3575268817204301</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2756410256410257</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1891025641025641</v>
+        <v>0.06720430107526881</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5352564102564102</v>
+        <v>0.3575268817204301</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2756410256410257</v>
+        <v>0.5752688172043011</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1891025641025641</v>
+        <v>0.06720430107526883</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Cerca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1928,34 +3264,535 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="n">
         <v>22</v>
       </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7806060606060605</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1587878787878788</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0606060606060606</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7806060606060606</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1587878787878788</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0875995449374289</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2411831626848692</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6712172923777019</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0875995449374289</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2411831626848692</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6712172923777019</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2075848303393213</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3153692614770459</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4770459081836327</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2075848303393213</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3153692614770459</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4770459081836327</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4826546003016591</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4012066365007541</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1161387631975867</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4826546003016591</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4012066365007542</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1161387631975867</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2289855072463768</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6985507246376811</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2289855072463768</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6985507246376811</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3671679197994987</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3671679197994987</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2656641604010025</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3671679197994988</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3671679197994988</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2656641604010025</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lejos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4570446735395188</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2714776632302405</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2714776632302405</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4570446735395189</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2714776632302406</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2714776632302406</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dinamismo_Demografico</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_municipios</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Baja</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Media</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>conteo_Alta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Baja</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Media</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P_manual_Alta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Baja</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Media</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P_pgmpy_Alta</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>max_dif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5042194092827004</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.390295358649789</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1054852320675105</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5042194092827005</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3902953586497891</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1054852320675106</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5034364261168385</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3178694158075601</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1786941580756014</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5034364261168385</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.3178694158075602</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1786941580756014</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>32</v>
+      </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1891025641025641</v>
+        <v>0.3688362919132149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5785256410256411</v>
+        <v>0.4220907297830375</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2323717948717949</v>
+        <v>0.2090729783037475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1891025641025641</v>
+        <v>0.3688362919132149</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5785256410256411</v>
+        <v>0.4220907297830375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2323717948717949</v>
+        <v>0.2090729783037475</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1964,88 +3801,88 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.561181434599156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3664825046040516</v>
+        <v>0.2194092827004219</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.2194092827004219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.5611814345991561</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3664825046040516</v>
+        <v>0.219409282700422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.219409282700422</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2349726775956284</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3087431693989071</v>
+        <v>0.4177083333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4562841530054645</v>
+        <v>0.4177083333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2349726775956284</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3087431693989071</v>
+        <v>0.4177083333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4562841530054645</v>
+        <v>0.4177083333333333</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -2054,43 +3891,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09068627450980392</v>
+        <v>0.348111658456486</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3553921568627451</v>
+        <v>0.1707717569786535</v>
       </c>
       <c r="I7" t="n">
-        <v>0.553921568627451</v>
+        <v>0.4811165845648603</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09068627450980392</v>
+        <v>0.348111658456486</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3553921568627451</v>
+        <v>0.1707717569786535</v>
       </c>
       <c r="L7" t="n">
-        <v>0.553921568627451</v>
+        <v>0.4811165845648603</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -2099,43 +3936,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
       <c r="G8" t="n">
-        <v>0.3205673758865248</v>
+        <v>0.357397504456328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3971631205673759</v>
+        <v>0.4055258467023173</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2822695035460993</v>
+        <v>0.2370766488413547</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3205673758865248</v>
+        <v>0.357397504456328</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3971631205673759</v>
+        <v>0.4055258467023173</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2822695035460993</v>
+        <v>0.2370766488413547</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -2144,43 +3981,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>11</v>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
       <c r="G9" t="n">
-        <v>0.3608562691131498</v>
+        <v>0.09980039920159679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3608562691131498</v>
+        <v>0.2075848303393213</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2782874617737003</v>
+        <v>0.6926147704590817</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3608562691131498</v>
+        <v>0.09980039920159679</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3608562691131498</v>
+        <v>0.2075848303393213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2782874617737003</v>
+        <v>0.6926147704590817</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2189,43 +4026,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2935103244837758</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1342182890855457</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5722713864306784</v>
+        <v>0.6554809843400446</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2935103244837758</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1342182890855457</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5722713864306784</v>
+        <v>0.6554809843400446</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -2321,28 +4158,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4374</v>
+        <v>354294</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3401560135125566</v>
+        <v>0.3411474368560099</v>
       </c>
       <c r="E2" t="n">
-        <v>0.332879130823649</v>
+        <v>0.3146662011155242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3269648556637945</v>
+        <v>0.3441863620284658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3401560135125564</v>
+        <v>0.3411474368560056</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3328791308236484</v>
+        <v>0.3146662011155278</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3269648556637953</v>
+        <v>0.3441863620284666</v>
       </c>
       <c r="J2" t="n">
-        <v>8.326672684688674e-16</v>
+        <v>4.274358644806853e-15</v>
       </c>
     </row>
     <row r="3">
@@ -2357,28 +4194,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1458</v>
+        <v>118098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2595761291741089</v>
+        <v>0.3336556139651483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3586028273196372</v>
+        <v>0.3093917258135351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3818210435062538</v>
+        <v>0.3569526602213166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2595761291741089</v>
+        <v>0.333655613965148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3586028273196373</v>
+        <v>0.3093917258135361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3818210435062539</v>
+        <v>0.3569526602213159</v>
       </c>
       <c r="J3" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>9.436895709313831e-16</v>
       </c>
     </row>
     <row r="4">
@@ -2393,28 +4230,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>729</v>
+        <v>59049</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362948991380541</v>
+        <v>0.3539091404301904</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3237637659883437</v>
+        <v>0.3295663306222213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3132872426311153</v>
+        <v>0.3165245289475882</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3629489913805407</v>
+        <v>0.3539091404301929</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3237637659883438</v>
+        <v>0.3295663306222221</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3132872426311155</v>
+        <v>0.3165245289475851</v>
       </c>
       <c r="J4" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>3.108624468950438e-15</v>
       </c>
     </row>
     <row r="5">
@@ -2425,29 +4262,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Distancia_Madrid=Cerca; Talento=Alto; Acceso_Ferroviario=Si; Coste_Inmobiliario=Alto; Renta=Alta; Especializacion_Servicios=Alta; Dinamismo_Demografico=Alto</t>
+          <t>Distancia_Madrid=Cerca; Talento=Alto; Acceso_Ferroviario=Si; Coste_Inmobiliario=Alto; Renta=Alta; Especializacion_Servicios=Alta; Dinamismo_Demografico=Alto; Densidad=Alta; Juventud=Alta; Sanidad=Media; Paro=Bajo</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2935103244837758</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1342182890855457</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5722713864306784</v>
+        <v>0.6554809843400448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2935103244837758</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1342182890855457</v>
+        <v>0.1722595078299776</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5722713864306784</v>
+        <v>0.6554809843400448</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2464,7 +4301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2475,8 +4312,12 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2522,10 +4363,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sanidad</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Paro</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Viabilidad_Empresarial</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>nombre_iecm</t>
         </is>
@@ -2579,6 +4440,26 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Acebeda (La)</t>
         </is>
       </c>
@@ -2626,10 +4507,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Ajalvir</t>
         </is>
@@ -2678,10 +4579,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Alameda del Valle</t>
         </is>
@@ -2735,6 +4656,26 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Álamo (El)</t>
         </is>
       </c>
@@ -2782,10 +4723,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Alcalá de Henares</t>
         </is>
@@ -2834,10 +4795,30 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Alcobendas</t>
         </is>
@@ -2886,10 +4867,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Alcorcón</t>
         </is>
@@ -2938,10 +4939,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Aldea del Fresno</t>
         </is>
@@ -2990,10 +5011,30 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Algete</t>
         </is>
@@ -3047,6 +5088,26 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Alpedrete</t>
         </is>
       </c>
@@ -3094,10 +5155,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Ambite</t>
         </is>
@@ -3151,6 +5232,26 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>Anchuelo</t>
         </is>
       </c>
@@ -3198,10 +5299,30 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Aranjuez</t>
         </is>
@@ -3250,10 +5371,30 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Arganda del Rey</t>
         </is>
@@ -3307,6 +5448,26 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>Arroyomolinos</t>
         </is>
       </c>
@@ -3359,6 +5520,26 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Atazar (El)</t>
         </is>
       </c>
@@ -3406,10 +5587,30 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Batres</t>
         </is>
@@ -3458,10 +5659,30 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Becerril de la Sierra</t>
         </is>
@@ -3510,10 +5731,30 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Belmonte de Tajo</t>
         </is>
@@ -3562,10 +5803,30 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Berzosa del Lozoya</t>
         </is>
@@ -3614,10 +5875,30 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Berrueco (El)</t>
         </is>
@@ -3671,6 +5952,26 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>Boadilla del Monte</t>
         </is>
       </c>
@@ -3718,10 +6019,30 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Boalo (El)</t>
         </is>
@@ -3775,6 +6096,26 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>Braojos</t>
         </is>
       </c>
@@ -3827,6 +6168,26 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>Brea de Tajo</t>
         </is>
       </c>
@@ -3879,6 +6240,26 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>Brunete</t>
         </is>
       </c>
@@ -3926,10 +6307,30 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Buitrago del Lozoya</t>
         </is>
@@ -3978,10 +6379,30 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bustarviejo</t>
         </is>
@@ -4035,6 +6456,26 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>Cabanillas de la Sierra</t>
         </is>
       </c>
@@ -4082,10 +6523,30 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>Cabrera (La)</t>
         </is>
@@ -4134,10 +6595,30 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Cadalso de los Vidrios</t>
         </is>
@@ -4186,10 +6667,30 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Camarma de Esteruelas</t>
         </is>
@@ -4238,10 +6739,30 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Campo Real</t>
         </is>
@@ -4295,6 +6816,26 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>Canencia</t>
         </is>
       </c>
@@ -4342,10 +6883,30 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>Carabaña</t>
         </is>
@@ -4399,6 +6960,26 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Casarrubuelos</t>
         </is>
       </c>
@@ -4451,6 +7032,26 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>Cenicientos</t>
         </is>
       </c>
@@ -4498,10 +7099,30 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Cercedilla</t>
         </is>
@@ -4555,6 +7176,26 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>Cervera de Buitrago</t>
         </is>
       </c>
@@ -4602,10 +7243,30 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>Ciempozuelos</t>
         </is>
@@ -4654,10 +7315,30 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>Cobeña</t>
         </is>
@@ -4711,6 +7392,26 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>Colmenar del Arroyo</t>
         </is>
       </c>
@@ -4763,6 +7464,26 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Colmenar de Oreja</t>
         </is>
       </c>
@@ -4815,6 +7536,26 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>Colmenarejo</t>
         </is>
       </c>
@@ -4867,6 +7608,26 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>Colmenar Viejo</t>
         </is>
       </c>
@@ -4919,6 +7680,26 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>Collado Mediano</t>
         </is>
       </c>
@@ -4966,10 +7747,30 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Collado Villalba</t>
         </is>
@@ -5023,6 +7824,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>Corpa</t>
         </is>
       </c>
@@ -5070,10 +7891,30 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>Coslada</t>
         </is>
@@ -5127,6 +7968,26 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Cubas de la Sagra</t>
         </is>
       </c>
@@ -5174,10 +8035,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>Chapinería</t>
         </is>
@@ -5231,6 +8112,26 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>Chinchón</t>
         </is>
       </c>
@@ -5283,6 +8184,26 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>Daganzo de Arriba</t>
         </is>
       </c>
@@ -5335,6 +8256,26 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>Escorial (El)</t>
         </is>
       </c>
@@ -5382,10 +8323,30 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>Estremera</t>
         </is>
@@ -5439,6 +8400,26 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>Fresnedillas de la Oliva</t>
         </is>
       </c>
@@ -5486,10 +8467,30 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>Fresno de Torote</t>
         </is>
@@ -5538,10 +8539,30 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>Fuenlabrada</t>
         </is>
@@ -5595,6 +8616,26 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
           <t>Fuente el Saz de Jarama</t>
         </is>
       </c>
@@ -5642,10 +8683,30 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>Fuentidueña de Tajo</t>
         </is>
@@ -5694,10 +8755,30 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>Galapagar</t>
         </is>
@@ -5751,6 +8832,26 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t>Garganta de los Montes</t>
         </is>
       </c>
@@ -5798,10 +8899,30 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Gargantilla del Lozoya y Pinilla de Buitrago</t>
         </is>
@@ -5850,10 +8971,30 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>Gascones</t>
         </is>
@@ -5907,6 +9048,26 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>Getafe</t>
         </is>
       </c>
@@ -5954,10 +9115,30 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>Griñón</t>
         </is>
@@ -6006,10 +9187,30 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>Guadalix de la Sierra</t>
         </is>
@@ -6063,6 +9264,26 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>Guadarrama</t>
         </is>
       </c>
@@ -6110,10 +9331,30 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>Hiruela (La)</t>
         </is>
@@ -6167,6 +9408,26 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t>Horcajo de la Sierra-Aoslos</t>
         </is>
       </c>
@@ -6214,10 +9475,30 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>Horcajuelo de la Sierra</t>
         </is>
@@ -6271,6 +9552,26 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
           <t>Hoyo de Manzanares</t>
         </is>
       </c>
@@ -6318,10 +9619,30 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>Humanes de Madrid</t>
         </is>
@@ -6370,10 +9691,30 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>Leganés</t>
         </is>
@@ -6422,10 +9763,30 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>Loeches</t>
         </is>
@@ -6474,10 +9835,30 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>Lozoya</t>
         </is>
@@ -6526,10 +9907,30 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>Madarcos</t>
         </is>
@@ -6578,10 +9979,30 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
@@ -6630,10 +10051,30 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>Majadahonda</t>
         </is>
@@ -6682,10 +10123,30 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>Manzanares el Real</t>
         </is>
@@ -6739,6 +10200,26 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t>Meco</t>
         </is>
       </c>
@@ -6786,10 +10267,30 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>Mejorada del Campo</t>
         </is>
@@ -6838,10 +10339,30 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>Miraflores de la Sierra</t>
         </is>
@@ -6895,6 +10416,26 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>Molar (El)</t>
         </is>
       </c>
@@ -6947,6 +10488,26 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Molinos (Los)</t>
         </is>
       </c>
@@ -6999,6 +10560,26 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
           <t>Montejo de la Sierra</t>
         </is>
       </c>
@@ -7046,10 +10627,30 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>Moraleja de Enmedio</t>
         </is>
@@ -7103,6 +10704,26 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
           <t>Moralzarzal</t>
         </is>
       </c>
@@ -7155,6 +10776,26 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
           <t>Morata de Tajuña</t>
         </is>
       </c>
@@ -7202,10 +10843,30 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>Móstoles</t>
         </is>
@@ -7259,6 +10920,26 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
           <t>Navacerrada</t>
         </is>
       </c>
@@ -7311,6 +10992,26 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>Navalafuente</t>
         </is>
       </c>
@@ -7363,6 +11064,26 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
           <t>Navalagamella</t>
         </is>
       </c>
@@ -7415,6 +11136,26 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>Navalcarnero</t>
         </is>
       </c>
@@ -7467,6 +11208,26 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Navarredonda y San Mamés</t>
         </is>
       </c>
@@ -7514,10 +11275,30 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>Navas del Rey</t>
         </is>
@@ -7571,6 +11352,26 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>Nuevo Baztán</t>
         </is>
       </c>
@@ -7623,6 +11424,26 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
           <t>Olmeda de las Fuentes</t>
         </is>
       </c>
@@ -7670,10 +11491,30 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>Orusco de Tajuña</t>
         </is>
@@ -7722,10 +11563,30 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>Paracuellos de Jarama</t>
         </is>
@@ -7779,6 +11640,26 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
           <t>Parla</t>
         </is>
       </c>
@@ -7826,10 +11707,30 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>Patones</t>
         </is>
@@ -7878,10 +11779,30 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>Pedrezuela</t>
         </is>
@@ -7935,6 +11856,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>Pelayos de la Presa</t>
         </is>
       </c>
@@ -7987,6 +11928,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>Perales de Tajuña</t>
         </is>
       </c>
@@ -8034,10 +11995,30 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>Pezuela de las Torres</t>
         </is>
@@ -8086,10 +12067,30 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>Pinilla del Valle</t>
         </is>
@@ -8138,10 +12139,30 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>Pinto</t>
         </is>
@@ -8195,6 +12216,26 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>Piñuécar-Gandullas</t>
         </is>
       </c>
@@ -8242,10 +12283,30 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>Pozuelo de Alarcón</t>
         </is>
@@ -8294,10 +12355,30 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>Pozuelo del Rey</t>
         </is>
@@ -8346,10 +12427,30 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>Prádena del Rincón</t>
         </is>
@@ -8398,10 +12499,30 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>Puebla de la Sierra</t>
         </is>
@@ -8450,10 +12571,30 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>Quijorna</t>
         </is>
@@ -8507,6 +12648,26 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>Rascafría</t>
         </is>
       </c>
@@ -8559,6 +12720,26 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
           <t>Redueña</t>
         </is>
       </c>
@@ -8606,10 +12787,30 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>Ribatejada</t>
         </is>
@@ -8663,6 +12864,26 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
           <t>Rivas-Vaciamadrid</t>
         </is>
       </c>
@@ -8710,10 +12931,30 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>Robledillo de la Jara</t>
         </is>
@@ -8762,10 +13003,30 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>Robledo de Chavela</t>
         </is>
@@ -8814,10 +13075,30 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>Robregordo</t>
         </is>
@@ -8866,10 +13147,30 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>Rozas de Madrid (Las)</t>
         </is>
@@ -8918,10 +13219,30 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>Rozas de Puerto Real</t>
         </is>
@@ -8970,10 +13291,30 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>San Agustín del Guadalix</t>
         </is>
@@ -9022,10 +13363,30 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>San Fernando de Henares</t>
         </is>
@@ -9074,10 +13435,30 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>San Lorenzo de El Escorial</t>
         </is>
@@ -9131,6 +13512,26 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
           <t>San Martín de la Vega</t>
         </is>
       </c>
@@ -9178,10 +13579,30 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>San Martín de Valdeiglesias</t>
         </is>
@@ -9230,10 +13651,30 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>San Sebastián de los Reyes</t>
         </is>
@@ -9282,10 +13723,30 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>Santa María de la Alameda</t>
         </is>
@@ -9334,10 +13795,30 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>Santorcaz</t>
         </is>
@@ -9386,10 +13867,30 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>Santos de la Humosa (Los)</t>
         </is>
@@ -9443,6 +13944,26 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
           <t>Serna del Monte (La)</t>
         </is>
       </c>
@@ -9495,6 +14016,26 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
           <t>Serranillos del Valle</t>
         </is>
       </c>
@@ -9542,10 +14083,30 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>Sevilla la Nueva</t>
         </is>
@@ -9599,6 +14160,26 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
           <t>Somosierra</t>
         </is>
       </c>
@@ -9646,10 +14227,30 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>Soto del Real</t>
         </is>
@@ -9698,10 +14299,30 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>Talamanca de Jarama</t>
         </is>
@@ -9755,6 +14376,26 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
           <t>Tielmes</t>
         </is>
       </c>
@@ -9802,10 +14443,30 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>Titulcia</t>
         </is>
@@ -9854,10 +14515,30 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>Torrejón de Ardoz</t>
         </is>
@@ -9911,6 +14592,26 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
           <t>Torrejón de la Calzada</t>
         </is>
       </c>
@@ -9958,10 +14659,30 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>Torrejón de Velasco</t>
         </is>
@@ -10010,10 +14731,30 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>Torrelaguna</t>
         </is>
@@ -10067,6 +14808,26 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
           <t>Torrelodones</t>
         </is>
       </c>
@@ -10119,6 +14880,26 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
           <t>Torremocha de Jarama</t>
         </is>
       </c>
@@ -10166,10 +14947,30 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>Torres de la Alameda</t>
         </is>
@@ -10223,6 +15024,26 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
           <t>Valdaracete</t>
         </is>
       </c>
@@ -10270,10 +15091,30 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>Valdeavero</t>
         </is>
@@ -10322,10 +15163,30 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>Valdelaguna</t>
         </is>
@@ -10374,10 +15235,30 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>Valdemanco</t>
         </is>
@@ -10431,6 +15312,26 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
           <t>Valdemaqueda</t>
         </is>
       </c>
@@ -10478,10 +15379,30 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>Valdemorillo</t>
         </is>
@@ -10535,6 +15456,26 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
           <t>Valdemoro</t>
         </is>
       </c>
@@ -10587,6 +15528,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
           <t>Valdeolmos-Alalpardo</t>
         </is>
       </c>
@@ -10634,10 +15595,30 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>Valdepiélagos</t>
         </is>
@@ -10686,10 +15667,30 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>Valdetorres de Jarama</t>
         </is>
@@ -10738,10 +15739,30 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>Valdilecha</t>
         </is>
@@ -10790,10 +15811,30 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>Valverde de Alcalá</t>
         </is>
@@ -10842,10 +15883,30 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>Velilla de San Antonio</t>
         </is>
@@ -10894,10 +15955,30 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>Vellón (El)</t>
         </is>
@@ -10951,6 +16032,26 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
           <t>Venturada</t>
         </is>
       </c>
@@ -10998,10 +16099,30 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>Villaconejos</t>
         </is>
@@ -11050,10 +16171,30 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>Villa del Prado</t>
         </is>
@@ -11107,6 +16248,26 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
           <t>Villalbilla</t>
         </is>
       </c>
@@ -11159,6 +16320,26 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
           <t>Villamanrique de Tajo</t>
         </is>
       </c>
@@ -11211,6 +16392,26 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
           <t>Villamanta</t>
         </is>
       </c>
@@ -11263,6 +16464,26 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
           <t>Villamantilla</t>
         </is>
       </c>
@@ -11315,6 +16536,26 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
           <t>Villanueva de la Cañada</t>
         </is>
       </c>
@@ -11367,6 +16608,26 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
           <t>Villanueva del Pardillo</t>
         </is>
       </c>
@@ -11419,6 +16680,26 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
           <t>Villanueva de Perales</t>
         </is>
       </c>
@@ -11466,10 +16747,30 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
         <is>
           <t>Villar del Olmo</t>
         </is>
@@ -11518,10 +16819,30 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>Villarejo de Salvanés</t>
         </is>
@@ -11570,10 +16891,30 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
         <is>
           <t>Villaviciosa de Odón</t>
         </is>
@@ -11622,10 +16963,30 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
         <is>
           <t>Villavieja del Lozoya</t>
         </is>
@@ -11674,10 +17035,30 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
         <is>
           <t>Zarzalejo</t>
         </is>
@@ -11726,10 +17107,30 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
         <is>
           <t>Lozoyuela-Navas-Sieteiglesias</t>
         </is>
@@ -11783,6 +17184,26 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
           <t>Puentes Viejas</t>
         </is>
       </c>
@@ -11830,10 +17251,30 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>Tres Cantos</t>
         </is>
@@ -11850,7 +17291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -12120,30 +17561,158 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>densidad_hab_km2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>terciles</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>['Baja', 'Media', 'Alta']</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[61.4524624606903, 249.0263253257394]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[60, 59, 60]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pct_menores_45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>terciles</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>['Baja', 'Media', 'Alta']</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[47.67666666666666, 51.88666666666666]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[60, 59, 60]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sanidad</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sanidad_por_1000hab</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>terciles</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>['Baja', 'Media', 'Alta']</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[0.2828747985508095, 0.6137146529534996]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[60, 59, 60]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Paro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>paro_por_100hab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>terciles</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>['Bajo', 'Medio', 'Alto']</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[4.053333333333333, 5.213333333333333]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[60, 59, 60]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Viabilidad_Empresarial</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>tasa_neta_emp</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>terciles</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>['Baja', 'Media', 'Alta']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>[0.005957543747997433, 0.0097648453382144]</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[60, 59, 60]</t>
         </is>
@@ -12247,22 +17816,22 @@
         <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3298059964726632</v>
+        <v>0.3304221251819505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3298059964726632</v>
+        <v>0.3304221251819505</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -12366,22 +17935,22 @@
         <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3298059964726632</v>
+        <v>0.3304221251819505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3298059964726632</v>
+        <v>0.3304221251819505</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3350970017636685</v>
+        <v>0.3347889374090248</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -12409,7 +17978,7 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12475,19 +18044,19 @@
         <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5473684210526315</v>
+        <v>0.5391304347826087</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4526315789473684</v>
+        <v>0.4608695652173913</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5473684210526316</v>
+        <v>0.5391304347826087</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4526315789473685</v>
+        <v>0.4608695652173913</v>
       </c>
       <c r="I2" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -12506,19 +18075,19 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8370044052863436</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1629955947136564</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8370044052863436</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09090909090909093</v>
+        <v>0.1629955947136564</v>
       </c>
       <c r="I3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -12537,19 +18106,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9263157894736841</v>
+        <v>0.8521739130434781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0736842105263158</v>
+        <v>0.1478260869565217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.8521739130434783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0736842105263158</v>
+        <v>0.1478260869565218</v>
       </c>
       <c r="I4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
   </sheetData>
@@ -12572,13 +18141,13 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12672,25 +18241,25 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2173112338858195</v>
+        <v>0.2383107088989442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6151012891344383</v>
+        <v>0.564102564102564</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1675874769797422</v>
+        <v>0.1975867269984917</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2173112338858195</v>
+        <v>0.2383107088989442</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6151012891344383</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1675874769797422</v>
+        <v>0.1975867269984917</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="3">
@@ -12717,22 +18286,22 @@
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08505747126436781</v>
+        <v>0.1387387387387387</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2091954022988506</v>
+        <v>0.236036036036036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7057471264367816</v>
+        <v>0.6252252252252252</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08505747126436781</v>
+        <v>0.1387387387387387</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2091954022988506</v>
+        <v>0.236036036036036</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7057471264367816</v>
+        <v>0.6252252252252252</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -12762,22 +18331,22 @@
         <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01366120218579235</v>
+        <v>0.05868544600938967</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08743169398907104</v>
+        <v>0.1220657276995305</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8989071038251366</v>
+        <v>0.8192488262910798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01366120218579235</v>
+        <v>0.05868544600938967</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08743169398907104</v>
+        <v>0.1220657276995305</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8989071038251366</v>
+        <v>0.8192488262910798</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -12807,25 +18376,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5385964912280702</v>
+        <v>0.5028985507246376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.443859649122807</v>
+        <v>0.4246376811594202</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5385964912280702</v>
+        <v>0.5028985507246377</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443859649122807</v>
+        <v>0.4246376811594203</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="6">
@@ -12852,25 +18421,25 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1596491228070175</v>
+        <v>0.1898550724637681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5859649122807018</v>
+        <v>0.5420289855072463</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2543859649122807</v>
+        <v>0.2681159420289855</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1596491228070175</v>
+        <v>0.1898550724637681</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5859649122807018</v>
+        <v>0.5420289855072464</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2543859649122807</v>
+        <v>0.2681159420289855</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="7">
@@ -12897,22 +18466,22 @@
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01841620626151013</v>
+        <v>0.07541478129713423</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.3197586726998491</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6648250460405156</v>
+        <v>0.6048265460030166</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01841620626151013</v>
+        <v>0.07541478129713423</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3167587476979742</v>
+        <v>0.3197586726998491</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6648250460405156</v>
+        <v>0.6048265460030166</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -12942,25 +18511,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7855946398659966</v>
+        <v>0.709902370990237</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1976549413735343</v>
+        <v>0.2203626220362622</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01675041876046901</v>
+        <v>0.0697350069735007</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7855946398659966</v>
+        <v>0.7099023709902371</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1976549413735343</v>
+        <v>0.2203626220362622</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01675041876046901</v>
+        <v>0.0697350069735007</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="9">
@@ -12987,25 +18556,25 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.532448377581121</v>
+        <v>0.5025062656641603</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3731563421828908</v>
+        <v>0.3671679197994987</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0943952802359882</v>
+        <v>0.1303258145363408</v>
       </c>
       <c r="J9" t="n">
-        <v>0.532448377581121</v>
+        <v>0.5025062656641605</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3731563421828908</v>
+        <v>0.3671679197994988</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0943952802359882</v>
+        <v>0.1303258145363409</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
     <row r="10">
@@ -13032,25 +18601,25 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7057471264367816</v>
+        <v>0.6252252252252252</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7057471264367816</v>
+        <v>0.6252252252252253</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1471264367816092</v>
+        <v>0.1873873873873874</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
   </sheetData>
@@ -13072,12 +18641,12 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -13162,25 +18731,25 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.775438596491228</v>
+        <v>0.6985507246376813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1912280701754386</v>
+        <v>0.2159420289855073</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0855072463768116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.775438596491228</v>
+        <v>0.6985507246376811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1912280701754386</v>
+        <v>0.2159420289855073</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.08550724637681159</v>
       </c>
       <c r="L2" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
     <row r="3">
@@ -13202,25 +18771,25 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2103386809269162</v>
+        <v>0.2320117474302497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6114081996434938</v>
+        <v>0.5624082232011748</v>
       </c>
       <c r="H3" t="n">
-        <v>0.17825311942959</v>
+        <v>0.2055800293685756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2103386809269162</v>
+        <v>0.2320117474302496</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6114081996434937</v>
+        <v>0.5624082232011748</v>
       </c>
       <c r="K3" t="n">
-        <v>0.17825311942959</v>
+        <v>0.2055800293685756</v>
       </c>
       <c r="L3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="4">
@@ -13242,25 +18811,25 @@
         <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.07246376811594203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1912280701754386</v>
+        <v>0.2159420289855073</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7912280701754386</v>
+        <v>0.7115942028985508</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01754385964912281</v>
+        <v>0.07246376811594202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1912280701754386</v>
+        <v>0.2159420289855073</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7912280701754386</v>
+        <v>0.7115942028985507</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
     </row>
   </sheetData>
